--- a/output/pdf_financials_xlsx/RPX.xlsx
+++ b/output/pdf_financials_xlsx/RPX.xlsx
@@ -4463,40 +4463,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.650508</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.160053</v>
+        <v>7.916906</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.318813</v>
+        <v>8.883635</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>7.642199</v>
+        <v>16.104763</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>7.658688</v>
+        <v>16.493563</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>8.043575000000001</v>
+        <v>11.34952</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>8.116146000000001</v>
+        <v>9.998799</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>8.353339999999999</v>
+        <v>10.241962</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>8.953310999999999</v>
+        <v>10.437995</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>9.541905</v>
+        <v>11.301806</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>9.690026</v>
+        <v>10.180238</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>10.0067</v>
+        <v>12.659003</v>
       </c>
     </row>
     <row r="93">
@@ -7952,7 +7952,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10466,7 +10470,11 @@
           <t>Warrant Reserve (note 9)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -11742,7 +11750,11 @@
           <t>Warrant Reserve (note 11)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -13090,7 +13102,11 @@
           <t>Warrant Reserve (note 14)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -13836,7 +13852,11 @@
           <t>Warrant Reserve (note 12)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -14444,7 +14464,11 @@
           <t>Warrant Reserve (note 13)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -15764,7 +15788,11 @@
           <t>Reserves (notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="n">
         <v>7.650508</v>
       </c>

--- a/output/pdf_financials_xlsx/RPX.xlsx
+++ b/output/pdf_financials_xlsx/RPX.xlsx
@@ -812,37 +812,37 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>2.702558</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1.569777</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>25.602314</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>4.134289</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>4.980046</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>3.94578</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>16.473562</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>13.387984</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>11.549564</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>7.694691</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>9.836919999999999</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.07613</v>
+        <v>-1.493647</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-4.134289</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-4.980046</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-3.94578</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-16.473562</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-7.694691</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-9.836919999999999</v>
       </c>
     </row>
     <row r="12">
@@ -909,16 +909,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000102</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000476</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009638000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -927,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.021693</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.059059</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.256139</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.214318</v>
       </c>
     </row>
     <row r="13">
@@ -1610,16 +1610,16 @@
         <v>-5.405116</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.493647</v>
+        <v>-1.493545</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-25.602314</v>
+        <v>-25.601838</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.834289</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.980046</v>
+        <v>-4.970408</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.94578</v>
@@ -1628,16 +1628,16 @@
         <v>-16.473562</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-11.096767</v>
+        <v>-11.075074</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.773852</v>
+        <v>-10.714793</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.504932</v>
+        <v>-6.248793</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.44739</v>
+        <v>-9.233072</v>
       </c>
     </row>
     <row r="28">
@@ -1696,16 +1696,16 @@
         <v>-5.396536</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.48318</v>
+        <v>-1.483078</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-25.535679</v>
+        <v>-25.535203</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.727945</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.871741</v>
+        <v>-4.862103</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-3.778548</v>
@@ -1714,16 +1714,16 @@
         <v>-16.362632</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-11.096767</v>
+        <v>-11.075074</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.773852</v>
+        <v>-10.714793</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.504932</v>
+        <v>-6.248793</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.44739</v>
+        <v>-9.233072</v>
       </c>
     </row>
     <row r="30">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1948.220149743859</v>
+        <v>-1948.086168396165</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.93248</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.115229</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0025</v>
+        <v>1.93498</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.117729</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.963914</v>
+        <v>0.031434</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.107814</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.110418</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.110419</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.114849</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.080843</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.184587</v>
       </c>
     </row>
     <row r="125">
@@ -5868,22 +5868,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.107814</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.110418</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.110419</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.114849</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.080843</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.184587</v>
       </c>
     </row>
     <row r="126">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -17272,7 +17272,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -24056,7 +24060,11 @@
           <t>Lease payments (note 4)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -40328,7 +40336,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -40622,7 +40630,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -43030,7 +43038,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -43856,7 +43864,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -44008,7 +44016,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -45740,7 +45748,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -45968,7 +45976,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">

--- a/output/pdf_financials_xlsx/RPX.xlsx
+++ b/output/pdf_financials_xlsx/RPX.xlsx
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.022509</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>0.67425</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.295115</v>
+        <v>0.317624</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.803559</v>
@@ -2527,7 +2527,7 @@
         <v>0.371753</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.628189</v>
+        <v>0.60568</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.08931</v>
@@ -3240,13 +3240,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.696222</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.286898</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.324289</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -3369,13 +3369,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.023667</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.04448</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03021</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.022707</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.217829</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.022707</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6306,10 +6306,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.30917</v>
+        <v>-2.331877</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.129924</v>
+        <v>-2.134424</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.389074</v>
@@ -35772,7 +35772,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -38976,7 +38980,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E433" s="5" t="n">
         <v>0.217829</v>
       </c>
@@ -39052,7 +39060,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E434" s="5" t="n">
         <v>-0.022707</v>
       </c>
